--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2035_AP_utilization_share.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2035_AP_utilization_share.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,37 +449,52 @@
           <t>Share</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>72924.57260729918</v>
       </c>
       <c r="C2" t="n">
-        <v>469937</v>
+        <v>149481</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.4878517845565603</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16933.56294409442</v>
+        <v>2342.272729844568</v>
       </c>
       <c r="C3" t="n">
-        <v>655567</v>
+        <v>365886.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0258304077906521</v>
+        <v>0.006401637474584517</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -497,261 +512,283 @@
       <c r="D4" t="n">
         <v>0.07737642789927963</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21992.08849453591</v>
+        <v>82408.23698334489</v>
       </c>
       <c r="C5" t="n">
-        <v>25402</v>
+        <v>220020.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8657620854474416</v>
+        <v>0.3745481645490368</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22893.00991923308</v>
+        <v>16933.56294409442</v>
       </c>
       <c r="C6" t="n">
-        <v>74252</v>
+        <v>655567</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3083150611328056</v>
+        <v>0.0258304077906521</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>6102.855912789503</v>
       </c>
       <c r="C7" t="n">
-        <v>273560</v>
+        <v>43965</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.1388116891343001</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19178.35148457539</v>
+        <v>136498.1012382965</v>
       </c>
       <c r="C8" t="n">
-        <v>50804</v>
+        <v>405455</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3774968798633058</v>
+        <v>0.3366541323656053</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50748.87502887535</v>
+        <v>19178.35148457539</v>
       </c>
       <c r="C9" t="n">
-        <v>500419.4</v>
+        <v>50804</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1014126850974909</v>
+        <v>0.3774968798633058</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3919.551013521025</v>
+        <v>21992.08849453591</v>
       </c>
       <c r="C10" t="n">
-        <v>14655</v>
+        <v>25402</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2674548627445258</v>
+        <v>0.8657620854474416</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6102.855912789503</v>
+        <v>7999.018737591262</v>
       </c>
       <c r="C11" t="n">
-        <v>43965</v>
+        <v>39080</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1388116891343001</v>
+        <v>0.2046831816169719</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7999.018737591262</v>
+        <v>3919.551013521025</v>
       </c>
       <c r="C12" t="n">
-        <v>39080</v>
+        <v>14655</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2046831816169719</v>
+        <v>0.2674548627445258</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>82408.23698334489</v>
+        <v>133352.3829575628</v>
       </c>
       <c r="C13" t="n">
-        <v>220020.4</v>
+        <v>140688</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3745481645490368</v>
+        <v>0.9478589713235159</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>22893.00991923308</v>
       </c>
       <c r="C14" t="n">
-        <v>253531.5</v>
+        <v>74252</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.3083150611328056</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72924.57260729918</v>
+        <v>50748.87502887535</v>
       </c>
       <c r="C15" t="n">
-        <v>149481</v>
+        <v>500419.4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4878517845565603</v>
+        <v>0.1014126850974909</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>133352.3829575628</v>
+        <v>579182.7993030038</v>
       </c>
       <c r="C16" t="n">
-        <v>140688</v>
+        <v>2710100.3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9478589713235159</v>
+        <v>0.2137126804137116</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Total_EU</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>136498.1012382965</v>
+        <v>528433.9242741285</v>
       </c>
       <c r="C17" t="n">
-        <v>405455</v>
+        <v>2209680.9</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3366541323656053</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2342.272729844568</v>
-      </c>
-      <c r="C18" t="n">
-        <v>365886.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.006401637474584517</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>579182.7993030037</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3707128.8</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1562348735503886</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Total_EU</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>528433.9242741284</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2736772.4</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.1930865439428315</v>
+        <v>0.2391449029016491</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2035_AP_utilization_share.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2035_AP_utilization_share.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2035_AP_utilization_share.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2035_AP_utilization_share.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,17 +647,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7999.018737591262</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>39080</v>
+        <v>253531.5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2046831816169719</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -668,17 +668,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3919.551013521025</v>
+        <v>7999.018737591262</v>
       </c>
       <c r="C12" t="n">
-        <v>14655</v>
+        <v>39080</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2674548627445258</v>
+        <v>0.2046831816169719</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -689,17 +689,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>133352.3829575628</v>
+        <v>3919.551013521025</v>
       </c>
       <c r="C13" t="n">
-        <v>140688</v>
+        <v>14655</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9478589713235159</v>
+        <v>0.2674548627445258</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -710,17 +710,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22893.00991923308</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>74252</v>
+        <v>273560</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3083150611328056</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -731,17 +731,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50748.87502887535</v>
+        <v>133352.3829575628</v>
       </c>
       <c r="C15" t="n">
-        <v>500419.4</v>
+        <v>140688</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1014126850974909</v>
+        <v>0.9478589713235159</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -752,40 +752,103 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>579182.7993030038</v>
+        <v>22893.00991923308</v>
       </c>
       <c r="C16" t="n">
-        <v>2710100.3</v>
+        <v>74252</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2137126804137116</v>
+        <v>0.3083150611328056</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>royalblue</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>50748.87502887535</v>
+      </c>
+      <c r="C17" t="n">
+        <v>500419.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1014126850974909</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>469937</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>579182.7993030038</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3707128.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1562348735503886</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Total_EU</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B20" t="n">
         <v>528433.9242741285</v>
       </c>
-      <c r="C17" t="n">
-        <v>2209680.9</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.2391449029016491</v>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="C20" t="n">
+        <v>2736772.4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1930865439428315</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
